--- a/3D_Models/FilMachine_macchina_v6/docs/NuovaDistinta.xlsx
+++ b/3D_Models/FilMachine_macchina_v6/docs/NuovaDistinta.xlsx
@@ -410,7 +410,7 @@
     <t xml:space="preserve">perno folle a molla</t>
   </si>
   <si>
-    <t xml:space="preserve">Vite M3 x 6 a testa zigrinata (vite a mano)</t>
+    <t xml:space="preserve">Vite M3 x 10 a testa zigrinata (vite a mano)</t>
   </si>
   <si>
     <t xml:space="preserve">blocco delle due slitte della guida B14/B15 nelle fossette della barra B13</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">B14_slitta_DX</t>
   </si>
   <si>
-    <t xml:space="preserve">in piedi sulla coda; supporti solo dal piatto (sotto il piano e l'aletta); si blocca con una vite zigrinata M3 x 6</t>
+    <t xml:space="preserve">in piedi sulla coda; supporti solo dal piatto (sotto il mozzo e il cappuccio); si blocca con una vite zigrinata M3 x 10 nell'orecchia del mozzo</t>
   </si>
   <si>
     <t xml:space="preserve">B15_slitta_SX</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">piastra del motore (B23)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vite M3 x 6 a testa zigrinata</t>
+    <t xml:space="preserve">Vite M3 x 10 a testa zigrinata</t>
   </si>
   <si>
     <t xml:space="preserve">motoriduttore sulla piastra: nel riduttore entrano 4 mm; se i suoi fori sono meno profondi usare M3 x 6</t>
@@ -5452,17 +5452,17 @@
         <v>1</v>
       </c>
       <c r="C27" s="20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="D27" s="20" t="n">
         <f aca="false">B27*C27</f>
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>30</v>
+        <v>29.1</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="G27" s="20" t="n">
         <v>73</v>
@@ -5479,17 +5479,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="20" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="D28" s="20" t="n">
         <f aca="false">B28*C28</f>
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>30</v>
+        <v>29.1</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="G28" s="20" t="n">
         <v>73</v>
@@ -6757,7 +6757,7 @@
       <c r="C77" s="10"/>
       <c r="D77" s="22" t="n">
         <f aca="false">SUM(D6:D76)</f>
-        <v>2712.5</v>
+        <v>2713.1</v>
       </c>
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="D78" s="23" t="n">
         <f aca="false">D77*B3*D3/1000</f>
-        <v>1.7224375</v>
+        <v>1.7228185</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
